--- a/data/evals/calibration/judge_calibration_v1.xlsx
+++ b/data/evals/calibration/judge_calibration_v1.xlsx
@@ -442,6 +442,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -463,6 +464,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -512,6 +514,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
@@ -519,6 +522,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
@@ -1409,7 +1413,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H24" s="2" t="n">
@@ -1417,7 +1421,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>[graded by Claude, NOT blind, owner to review] form mentioned (not "filled and signed"): core claim present; owner rubric: strict reading, 2026-10-11</t>
+          <t>[graded by Claude, NOT blind, owner to review] form mentioned (not "filled and signed"): core claim present</t>
         </is>
       </c>
     </row>
@@ -1442,13 +1446,13 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H25" s="3" t="n"/>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>CIN copy mentioned (not "show original"): core claim present; owner rubric: strict reading, 2026-10-11</t>
+          <t>CIN copy mentioned (not "show original"): core claim present</t>
         </is>
       </c>
     </row>
@@ -1531,13 +1535,13 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H28" s="3" t="n"/>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>"دفع الرسوم المطلوبة": payment mentioned, borderline; owner rubric: strict reading, 2026-10-11</t>
+          <t>"دفع الرسوم المطلوبة": payment mentioned, borderline</t>
         </is>
       </c>
     </row>
@@ -1824,13 +1828,13 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H36" s="3" t="n"/>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>25 TND for a pupil with proof; 80 not mentioned. Borderline, the child is a pupil; owner rubric: strict reading, 2026-10-11</t>
+          <t>25 TND for a pupil with proof; 80 not mentioned. Borderline, the child is a pupil</t>
         </is>
       </c>
     </row>
